--- a/DATA KOPERASI.xlsx
+++ b/DATA KOPERASI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E772D8-19F5-494D-99C9-0F3907C89381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B958CAB-C23D-422D-9A59-0865A5ABCB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="723" activeTab="3" xr2:uid="{F970B87B-20DA-4A5C-AAEA-A159F2A492B1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" tabRatio="723" activeTab="1" xr2:uid="{F970B87B-20DA-4A5C-AAEA-A159F2A492B1}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet 1" sheetId="37" r:id="rId1"/>
@@ -14191,7 +14191,7 @@
         <v>159</v>
       </c>
       <c r="C237" s="7">
-        <v>5095000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
